--- a/01_Thermal/B_results/single_annular_var_analysis.xlsx
+++ b/01_Thermal/B_results/single_annular_var_analysis.xlsx
@@ -1,121 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hl3422_ic_ac_uk/Documents/Year 4/Final Year Project/01 - Github/Nausicaa/01_Thermal/B_results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B5960F71364A93CB319321159C868F642EFFC90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E252A203-B9A6-4CC7-BAD2-70E9B97B78A8}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="single_annular_var_analysis" sheetId="1" r:id="rId1"/>
+    <sheet name="single_annular_var_analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>sheet</t>
-  </si>
-  <si>
-    <t>z_m</t>
-  </si>
-  <si>
-    <t>n_samples</t>
-  </si>
-  <si>
-    <t>accumulate_SAE_mps</t>
-  </si>
-  <si>
-    <t>weighted_RMSE_mps</t>
-  </si>
-  <si>
-    <t>weight_sum_term</t>
-  </si>
-  <si>
-    <t>A_ring</t>
-  </si>
-  <si>
-    <t>r_ring</t>
-  </si>
-  <si>
-    <t>delta_r</t>
-  </si>
-  <si>
-    <t>w0</t>
-  </si>
-  <si>
-    <t>z020</t>
-  </si>
-  <si>
-    <t>z035</t>
-  </si>
-  <si>
-    <t>z050</t>
-  </si>
-  <si>
-    <t>z075</t>
-  </si>
-  <si>
-    <t>z110</t>
-  </si>
-  <si>
-    <t>z160</t>
-  </si>
-  <si>
-    <t>z220</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>weighted_SSE_term</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,29 +73,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -448,312 +451,358 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>z_m</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>n_samples</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>accumulate_SAE_mps</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>weighted_RMSE_mps</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>weighted_SSE_term</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>weight_sum_term</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>A_ring</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>r_ring</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>delta_r</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>w0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.2</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>195</v>
       </c>
-      <c r="D2">
-        <v>16.60568863680809</v>
-      </c>
-      <c r="E2">
-        <v>0.29463406329528052</v>
-      </c>
-      <c r="F2">
-        <v>1042.027672452725</v>
-      </c>
-      <c r="G2">
-        <v>12003.650503540921</v>
-      </c>
-      <c r="H2">
-        <v>5.0335229854216044</v>
-      </c>
-      <c r="I2">
-        <v>0.30577763455507673</v>
-      </c>
-      <c r="J2">
-        <v>0.21062049209018149</v>
-      </c>
-      <c r="K2">
-        <v>9.9999999999999788E-5</v>
+      <c r="D2" t="n">
+        <v>16.61640059095281</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2948135380630582</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1043.297550299491</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12003.65050354092</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.033052279130711</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3056239944714074</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.210752420248507</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.35</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>195</v>
       </c>
-      <c r="D3">
-        <v>8.8399652226959358</v>
-      </c>
-      <c r="E3">
-        <v>9.5712474512564219E-2</v>
-      </c>
-      <c r="F3">
-        <v>89.805857387431757</v>
-      </c>
-      <c r="G3">
-        <v>9803.1934897969368</v>
-      </c>
-      <c r="H3">
-        <v>4.5086018738772058</v>
-      </c>
-      <c r="I3">
-        <v>0.3275258006741637</v>
-      </c>
-      <c r="J3">
-        <v>0.2995575376532067</v>
-      </c>
-      <c r="K3">
-        <v>9.9999999999999991E-5</v>
+      <c r="D3" t="n">
+        <v>8.902229017104434</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.09615783802812436</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90.64356023950231</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9803.193489796937</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.497177416740473</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3274327497449923</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.300687128100693</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.5</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>195</v>
       </c>
-      <c r="D4">
-        <v>17.88618382384491</v>
-      </c>
-      <c r="E4">
-        <v>0.32831906537465649</v>
-      </c>
-      <c r="F4">
-        <v>979.94651573471924</v>
-      </c>
-      <c r="G4">
-        <v>9090.9688046572955</v>
-      </c>
-      <c r="H4">
-        <v>4.3769755649002793</v>
-      </c>
-      <c r="I4">
-        <v>0.50412053554850778</v>
-      </c>
-      <c r="J4">
-        <v>0.25642683063408539</v>
-      </c>
-      <c r="K4">
-        <v>9.9999999999999951E-5</v>
+      <c r="D4" t="n">
+        <v>17.90398499079509</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3287104397554931</v>
+      </c>
+      <c r="F4" t="n">
+        <v>982.2842085057972</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9090.968804657296</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.377473856881211</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5039237833082832</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2567002673970867</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>195</v>
       </c>
-      <c r="D5">
-        <v>13.57371934656568</v>
-      </c>
-      <c r="E5">
-        <v>9.648318938600936E-2</v>
-      </c>
-      <c r="F5">
-        <v>666.90461900923424</v>
-      </c>
-      <c r="G5">
-        <v>71640.799339337638</v>
-      </c>
-      <c r="H5">
-        <v>2.9374515667306009</v>
-      </c>
-      <c r="I5">
-        <v>0.35987923482795442</v>
-      </c>
-      <c r="J5">
-        <v>0.45106680703610402</v>
-      </c>
-      <c r="K5">
-        <v>9.9999999999999991E-5</v>
+      <c r="D5" t="n">
+        <v>13.23872751873169</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.09529403312547827</v>
+      </c>
+      <c r="F5" t="n">
+        <v>650.5667137240225</v>
+      </c>
+      <c r="G5" t="n">
+        <v>71640.79933933764</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.938255286145861</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3522596198447994</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4519849543278506</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C6" t="n">
         <v>195</v>
       </c>
-      <c r="D6">
-        <v>11.579281362161311</v>
-      </c>
-      <c r="E6">
-        <v>0.1372731435839408</v>
-      </c>
-      <c r="F6">
-        <v>302.38205818502053</v>
-      </c>
-      <c r="G6">
-        <v>16046.667741286121</v>
-      </c>
-      <c r="H6">
-        <v>2.4379134453995399</v>
-      </c>
-      <c r="I6">
-        <v>0.39678537485094162</v>
-      </c>
-      <c r="J6">
-        <v>0.42080748180541028</v>
-      </c>
-      <c r="K6">
-        <v>9.9999999999999788E-5</v>
+      <c r="D6" t="n">
+        <v>11.57982319720761</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1372480813912408</v>
+      </c>
+      <c r="F6" t="n">
+        <v>302.2716554446652</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16046.66774128612</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.435955988105618</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3963469909285288</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4213812543802276</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1.6</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>195</v>
       </c>
-      <c r="D7">
-        <v>10.480272830418491</v>
-      </c>
-      <c r="E7">
-        <v>0.2239057470787256</v>
-      </c>
-      <c r="F7">
-        <v>270.92581552129661</v>
-      </c>
-      <c r="G7">
-        <v>5404.0568295953326</v>
-      </c>
-      <c r="H7">
-        <v>2.6429721868139291</v>
-      </c>
-      <c r="I7">
-        <v>0.42480636651357218</v>
-      </c>
-      <c r="J7">
-        <v>0.42685645938770361</v>
-      </c>
-      <c r="K7">
-        <v>9.9999999999999137E-5</v>
+      <c r="D7" t="n">
+        <v>10.48009814423822</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2239067801211528</v>
+      </c>
+      <c r="F7" t="n">
+        <v>270.92831548846</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5404.056829595333</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.643112120016701</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4247967191274478</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4268515626110699</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.999999999999799e-05</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C8" t="n">
         <v>195</v>
       </c>
-      <c r="D8">
-        <v>8.8694385102533388</v>
-      </c>
-      <c r="E8">
-        <v>7.640539555644095E-2</v>
-      </c>
-      <c r="F8">
-        <v>113.98217634692089</v>
-      </c>
-      <c r="G8">
-        <v>19524.903142623469</v>
-      </c>
-      <c r="H8">
-        <v>2.0822792485605111</v>
-      </c>
-      <c r="I8">
-        <v>0.40566665662683138</v>
-      </c>
-      <c r="J8">
-        <v>0.51953661936030937</v>
-      </c>
-      <c r="K8">
-        <v>9.9999999999999991E-5</v>
+      <c r="D8" t="n">
+        <v>8.869891357944061</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07641447702857249</v>
+      </c>
+      <c r="F8" t="n">
+        <v>114.0092735818082</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19524.90314262347</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.082318135949508</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4056610221435744</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5195889724952394</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
         <v>1365</v>
       </c>
-      <c r="D9">
-        <v>87.834549732747746</v>
-      </c>
-      <c r="E9">
-        <v>0.15540507509100041</v>
-      </c>
-      <c r="F9">
-        <v>3465.9747146373479</v>
-      </c>
-      <c r="G9">
-        <v>143514.23985083771</v>
-      </c>
+      <c r="D9" t="n">
+        <v>87.5911548169739</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1551364143429908</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3454.001277283747</v>
+      </c>
+      <c r="G9" t="n">
+        <v>143514.2398508377</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/01_Thermal/B_results/single_annular_var_analysis.xlsx
+++ b/01_Thermal/B_results/single_annular_var_analysis.xlsx
@@ -529,28 +529,28 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61640059095281</v>
+        <v>29.58460950430673</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2948135380630582</v>
+        <v>0.2632962484405744</v>
       </c>
       <c r="F2" t="n">
-        <v>1043.297550299491</v>
+        <v>832.1520441602153</v>
       </c>
       <c r="G2" t="n">
         <v>12003.65050354092</v>
       </c>
       <c r="H2" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828835</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="J2" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="K2" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="3">
@@ -566,28 +566,28 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>8.902229017104434</v>
+        <v>10.39881377372211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09615783802812436</v>
+        <v>0.09466756543665755</v>
       </c>
       <c r="F3" t="n">
-        <v>90.64356023950231</v>
+        <v>87.85570975722291</v>
       </c>
       <c r="G3" t="n">
         <v>9803.193489796937</v>
       </c>
       <c r="H3" t="n">
-        <v>4.497177416740473</v>
+        <v>4.504554871688979</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3274327497449923</v>
+        <v>0.3280733407944455</v>
       </c>
       <c r="J3" t="n">
-        <v>0.300687128100693</v>
+        <v>0.2965147859884885</v>
       </c>
       <c r="K3" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01030739740961069</v>
       </c>
     </row>
     <row r="4">
@@ -603,28 +603,28 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>17.90398499079509</v>
+        <v>21.06587378303127</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3287104397554931</v>
+        <v>0.3277235755217277</v>
       </c>
       <c r="F4" t="n">
-        <v>982.2842085057972</v>
+        <v>976.3949766270671</v>
       </c>
       <c r="G4" t="n">
         <v>9090.968804657296</v>
       </c>
       <c r="H4" t="n">
-        <v>4.377473856881211</v>
+        <v>4.372379358174996</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5039237833082832</v>
+        <v>0.5034238703794722</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2567002673970867</v>
+        <v>0.2540811354115556</v>
       </c>
       <c r="K4" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02166117169207601</v>
       </c>
     </row>
     <row r="5">
@@ -640,28 +640,28 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>13.23872751873169</v>
+        <v>15.6595237501716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09529403312547827</v>
+        <v>0.09423592577366598</v>
       </c>
       <c r="F5" t="n">
-        <v>650.5667137240225</v>
+        <v>636.1996498287331</v>
       </c>
       <c r="G5" t="n">
         <v>71640.79933933764</v>
       </c>
       <c r="H5" t="n">
-        <v>2.938255286145861</v>
+        <v>3.007695963869996</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3522596198447994</v>
+        <v>0.3716909497932002</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4519849543278506</v>
+        <v>0.4232312347850639</v>
       </c>
       <c r="K5" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01755749358929044</v>
       </c>
     </row>
     <row r="6">
@@ -677,28 +677,28 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>11.57982319720761</v>
+        <v>12.92835259534872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1372480813912408</v>
+        <v>0.1370432953899561</v>
       </c>
       <c r="F6" t="n">
-        <v>302.2716554446652</v>
+        <v>301.3702975215656</v>
       </c>
       <c r="G6" t="n">
         <v>16046.66774128612</v>
       </c>
       <c r="H6" t="n">
-        <v>2.435955988105618</v>
+        <v>2.439214544628072</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3963469909285288</v>
+        <v>0.3987765170195623</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4213812543802276</v>
+        <v>0.4164259091130328</v>
       </c>
       <c r="K6" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009266379933207952</v>
       </c>
     </row>
     <row r="7">
@@ -714,28 +714,28 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>10.48009814423822</v>
+        <v>10.97575351462924</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2239067801211528</v>
+        <v>0.2234211835229902</v>
       </c>
       <c r="F7" t="n">
-        <v>270.92831548846</v>
+        <v>269.7544411981261</v>
       </c>
       <c r="G7" t="n">
         <v>5404.056829595333</v>
       </c>
       <c r="H7" t="n">
-        <v>2.643112120016701</v>
+        <v>2.64378362529128</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4247967191274478</v>
+        <v>0.4252089437250119</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4268515626110699</v>
+        <v>0.4249063398721223</v>
       </c>
       <c r="K7" t="n">
-        <v>9.999999999999799e-05</v>
+        <v>0.003354883256357605</v>
       </c>
     </row>
     <row r="8">
@@ -751,28 +751,28 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>8.869891357944061</v>
+        <v>9.820718687527974</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07641447702857249</v>
+        <v>0.07613726941861633</v>
       </c>
       <c r="F8" t="n">
-        <v>114.0092735818082</v>
+        <v>113.1835946171046</v>
       </c>
       <c r="G8" t="n">
         <v>19524.90314262347</v>
       </c>
       <c r="H8" t="n">
-        <v>2.082318135949508</v>
+        <v>2.080269377750964</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4056610221435744</v>
+        <v>0.4072136409778495</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5195889724952394</v>
+        <v>0.514327794546161</v>
       </c>
       <c r="K8" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.006925047336243084</v>
       </c>
     </row>
     <row r="9">
@@ -786,13 +786,13 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>87.5911548169739</v>
+        <v>110.4336456087376</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1551364143429908</v>
+        <v>0.1497173067528658</v>
       </c>
       <c r="F9" t="n">
-        <v>3454.001277283747</v>
+        <v>3216.910713710035</v>
       </c>
       <c r="G9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/single_annular_var_analysis.xlsx
+++ b/01_Thermal/B_results/single_annular_var_analysis.xlsx
@@ -529,28 +529,28 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>29.58460950430673</v>
+        <v>20.27000419219389</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2632962484405744</v>
+        <v>0.2800208354549308</v>
       </c>
       <c r="F2" t="n">
-        <v>832.1520441602153</v>
+        <v>941.2262615392672</v>
       </c>
       <c r="G2" t="n">
         <v>12003.65050354092</v>
       </c>
       <c r="H2" t="n">
-        <v>4.916295944828835</v>
+        <v>4.998802864841869</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064589361194576</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2079769127801623</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.03629658098881634</v>
       </c>
     </row>
     <row r="3">
@@ -566,28 +566,28 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>10.39881377372211</v>
+        <v>9.177345843833265</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09466756543665755</v>
+        <v>0.08622618395801604</v>
       </c>
       <c r="F3" t="n">
-        <v>87.85570975722291</v>
+        <v>72.88630049191828</v>
       </c>
       <c r="G3" t="n">
         <v>9803.193489796937</v>
       </c>
       <c r="H3" t="n">
-        <v>4.504554871688979</v>
+        <v>4.695956807537173</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3280733407944455</v>
+        <v>0.3385179975653352</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2965147859884885</v>
+        <v>0.2582306881344782</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01030739740961069</v>
+        <v>0.01196378362045562</v>
       </c>
     </row>
     <row r="4">
@@ -603,28 +603,28 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>21.06587378303127</v>
+        <v>20.44246255345664</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3277235755217277</v>
+        <v>0.327020384049187</v>
       </c>
       <c r="F4" t="n">
-        <v>976.3949766270671</v>
+        <v>972.2094003245312</v>
       </c>
       <c r="G4" t="n">
         <v>9090.968804657296</v>
       </c>
       <c r="H4" t="n">
-        <v>4.372379358174996</v>
+        <v>4.353854435962207</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5034238703794722</v>
+        <v>0.5044172041423595</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2540811354115556</v>
+        <v>0.2553461970637524</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02166117169207601</v>
+        <v>0.01780512869043718</v>
       </c>
     </row>
     <row r="5">
@@ -640,28 +640,28 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6595237501716</v>
+        <v>16.70866063948985</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09423592577366598</v>
+        <v>0.0956470250759192</v>
       </c>
       <c r="F5" t="n">
-        <v>636.1996498287331</v>
+        <v>655.3953506355307</v>
       </c>
       <c r="G5" t="n">
         <v>71640.79933933764</v>
       </c>
       <c r="H5" t="n">
-        <v>3.007695963869996</v>
+        <v>3.451656877238781</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3716909497932002</v>
+        <v>0.4348387568936503</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4232312347850639</v>
+        <v>0.3267280382704591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01755749358929044</v>
+        <v>0.01879372149375707</v>
       </c>
     </row>
     <row r="6">
@@ -677,28 +677,28 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>12.92835259534872</v>
+        <v>13.0202011698201</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1370432953899561</v>
+        <v>0.1393605819433304</v>
       </c>
       <c r="F6" t="n">
-        <v>301.3702975215656</v>
+        <v>311.6483003479038</v>
       </c>
       <c r="G6" t="n">
         <v>16046.66774128612</v>
       </c>
       <c r="H6" t="n">
-        <v>2.439214544628072</v>
+        <v>2.468610988828762</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3987765170195623</v>
+        <v>0.4053896694320459</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4164259091130328</v>
+        <v>0.4127997747244014</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009266379933207952</v>
+        <v>0.009188798956841958</v>
       </c>
     </row>
     <row r="7">
@@ -714,28 +714,28 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>10.97575351462924</v>
+        <v>10.82345044054665</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2234211835229902</v>
+        <v>0.2213758499144246</v>
       </c>
       <c r="F7" t="n">
-        <v>269.7544411981261</v>
+        <v>264.8380555276519</v>
       </c>
       <c r="G7" t="n">
         <v>5404.056829595333</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64378362529128</v>
+        <v>2.664365846347008</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4252089437250119</v>
+        <v>0.4278495287033554</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4249063398721223</v>
+        <v>0.4168107633914932</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003354883256357605</v>
+        <v>0.002843156979147734</v>
       </c>
     </row>
     <row r="8">
@@ -751,28 +751,28 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>9.820718687527974</v>
+        <v>9.683282999048519</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07613726941861633</v>
+        <v>0.07507751756013717</v>
       </c>
       <c r="F8" t="n">
-        <v>113.1835946171046</v>
+        <v>110.0547259298854</v>
       </c>
       <c r="G8" t="n">
         <v>19524.90314262347</v>
       </c>
       <c r="H8" t="n">
-        <v>2.080269377750964</v>
+        <v>2.067285179839442</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4072136409778495</v>
+        <v>0.4016776878135916</v>
       </c>
       <c r="J8" t="n">
-        <v>0.514327794546161</v>
+        <v>0.5175169624275751</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006925047336243084</v>
+        <v>0.006617695006858467</v>
       </c>
     </row>
     <row r="9">
@@ -786,13 +786,13 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>110.4336456087376</v>
+        <v>100.1254078383889</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1497173067528658</v>
+        <v>0.1522863650457671</v>
       </c>
       <c r="F9" t="n">
-        <v>3216.910713710035</v>
+        <v>3328.258394796688</v>
       </c>
       <c r="G9" t="n">
         <v>143514.2398508377</v>
